--- a/outputs/3413.xlsx
+++ b/outputs/3413.xlsx
@@ -410,7 +410,7 @@
         <v>6</v>
       </c>
       <c r="G3" s="4" t="n">
-        <f aca="false">SUMPRODUCT((A3:A7=E3)*(B3:B7=F3)*C3:C7)</f>
+        <f aca="false">IF(COUNTIFS($A$3:$A$7,E3,$B$3:$B$7,F3)&gt;0,SUMIFS($C$3:$C$7,$A$3:$A$7,E3,$B$3:$B$7,F3),SUMIFS($C$3:$C$7,$A$3:$A$7,E3))</f>
         <v>14</v>
       </c>
     </row>
@@ -431,7 +431,7 @@
         <v>8</v>
       </c>
       <c r="G4" s="4" t="n">
-        <f aca="false">SUMPRODUCT((A3:A7=E4)*C3:C7)</f>
+        <f aca="false">IF(COUNTIFS($A$3:$A$7,E4,$B$3:$B$7,F4)&gt;0,SUMIFS($C$3:$C$7,$A$3:$A$7,E4,$B$3:$B$7,F4),SUMIFS($C$3:$C$7,$A$3:$A$7,E4))</f>
         <v>27</v>
       </c>
     </row>
@@ -452,7 +452,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="4" t="n">
-        <f aca="false">SUMPRODUCT((A3:A7=E5)*(B3:B7=F5)*C3:C7)</f>
+        <f aca="false">IF(COUNTIFS($A$3:$A$7,E5,$B$3:$B$7,F5)&gt;0,SUMIFS($C$3:$C$7,$A$3:$A$7,E5,$B$3:$B$7,F5),SUMIFS($C$3:$C$7,$A$3:$A$7,E5))</f>
         <v>4</v>
       </c>
     </row>
@@ -473,7 +473,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="4" t="n">
-        <f aca="false">SUMPRODUCT((A3:A7=E6)*C3:C7)</f>
+        <f aca="false">IF(COUNTIFS($A$3:$A$7,E6,$B$3:$B$7,F6)&gt;0,SUMIFS($C$3:$C$7,$A$3:$A$7,E6,$B$3:$B$7,F6),SUMIFS($C$3:$C$7,$A$3:$A$7,E6))</f>
         <v>11</v>
       </c>
     </row>
